--- a/outputs/resultats/bmo/2025_t3_vs_2025_t2/comparison.xlsx
+++ b/outputs/resultats/bmo/2025_t3_vs_2025_t2/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,6 +523,21 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -544,31 +562,34 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Le ratio prêt/valeur (RPV) est fonction de l’encours initial des prêts hypothécaires et des montants autorisés pouvant être prélevés sur les marges de crédit sur valeur domiciliaire, divisés par la valeur de la garantie au moment du montage.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Région²</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The removal of the footnote explaining the calculation of the loan-to-value ratio (RPV) could lead to a lack of clarity regarding the methodology used for this important financial metric, potentially affecting the interpretation of the table's data.</t>
+          <t>Cet ajout structurel modifie la présentation des données, ce qui peut influencer l'interprétation des résultats régionaux.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -578,17 +599,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TABLEAU 37</t>
+          <t>TABLEAU 23</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -603,21 +624,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Valeur non exigée par la norme régissant les informations à fournir sur le RSLLT.</t>
+          <t>Le ratio prêt/valeur (RPV) est fonction de l’encours initial des prêts hypothécaires et des montants autorisés pouvant être prélevés sur les marges de crédit sur valeur domiciliaire, divisés par la valeur de la garantie au moment du montage.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The removal of this footnote could indicate a change in the regulatory requirements or reporting standards for the RSLLT, which may affect the bank's compliance obligations and the transparency of its disclosures.</t>
+          <t>La suppression de cette note supprime une explication importante sur le calcul du ratio prêt/valeur, ce qui peut affecter la compréhension des risques associés aux prêts hypothécaires.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -627,7 +651,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Actions en circulation et titres convertibles en actions ordinaires¹ TABLEAU 13</t>
+          <t>TABLEAU 13</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -658,15 +682,30 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The addition of a new series of debt instruments suggests a structural change in the capital management strategy, potentially impacting the bank's leverage and capital adequacy ratios.</t>
+          <t>Cet ajout reflète l'émission d'une nouvelle série de billets avec remboursement de capital à recours limité, ce qui peut avoir un impact sur la structure du capital et les obligations financières de l'institution.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06T12:17:52.414039+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -676,7 +715,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Actions en circulation et titres convertibles en actions ordinaires¹ TABLEAU 13</t>
+          <t>TABLEAU 13</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -701,25 +740,28 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 49, aux actions privilégiées, série 51, aux actions privilégiées, série 53 et aux actions privilégiées, série 54 au titre des billets avec remboursement de capital à recours limité, série 3, série 4 et série 5, respectivement émises en même temps que les billets avec remboursement de capital à recours limité, qui comprennent actuellement cette modalité.</t>
+          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 49, aux actions privilégiées, série 51, aux actions privilégiées, série 53 et aux actions privilégiées, série 54 au titre des billets avec remboursement de capital à recours limité, série 3, série 4 et série 5, respectivement émises en même temps que les billets avec remboursement de capital à recours limité, qui comprennent actuellement une clause de non-viabilité limitée.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 49, aux actions privilégiées, série 51, aux actions privilégiées, série 53, aux actions privilégiées, série 54 et aux actions privilégiées, capital à recours limité, série 1, série 2, série 3, série 4, série 5 et série 6, respectivement émises en même temps que les billets avec remboursement actuellement les actifs détenus dans une fiducie à recours limité.</t>
+          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 49, aux actions privilégiées, série 51, aux actions privilégiées, série 53, aux actions privilégiées, série 54 et aux actions privilégiées, à recours limité, série 1, série 2, série 3, série 4, série 5 et série 6, respectivement émises en même temps que les billets avec remboursement de capital à recours limité, actuellement les actifs détenus dans une fiducie à recours limité.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>The inclusion of additional series and clarification of the capital structure in the footnote indicates a significant change in the convertible instruments, which could impact the bank's capital strategy and regulatory compliance.</t>
+          <t>L'ajout des séries 1, 2 et 6 dans la note indique une extension des instruments convertibles, ce qui peut affecter la structure du capital et les droits des actionnaires.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -729,7 +771,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Actions en circulation et titres convertibles en actions ordinaires¹ TABLEAU 13</t>
+          <t>TABLEAU 13</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -760,63 +802,1081 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>The removal of a tranche from the capital structure could affect the bank's capital composition and funding strategy, which is significant for understanding changes in financial stability and regulatory compliance.</t>
+          <t>La suppression de cette tranche peut indiquer un changement dans la structure de financement ou le remboursement de cette série, ce qui est important pour l'analyse de la gestion du capital.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06T12:17:52.962372+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 25</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 25</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 26</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 26</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 27</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 27</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 28</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 28</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 29</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 29</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 30</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 30</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 31</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 31</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 32</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 32</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 33</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 33</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 34</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 34</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 35</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 35</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 36</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 36</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 37</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 37</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 38</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 38</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 39</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 39</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 40</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 40</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 41</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 41</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 42</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 42</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 43</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 43</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Réglementation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>TABLEAU 21</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>TABLEAU 21</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>L'ajout d'un nouveau tableau avec des indicateurs liés à l'activité transfrontière et à la complexité est pertinent pour la veille réglementaire.</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:N28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>